--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.1426083144935</v>
+        <v>11.3981738511052</v>
       </c>
       <c r="D2" t="n">
-        <v>70.30370990973837</v>
+        <v>11.42435286033249</v>
       </c>
       <c r="E2" t="n">
-        <v>1.370167287237663</v>
+        <v>0.2226521841761206</v>
       </c>
       <c r="F2" t="n">
-        <v>1.498361431223657</v>
+        <v>0.2434837325738446</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.40227374001817</v>
+        <v>10.95286948275295</v>
       </c>
       <c r="D3" t="n">
-        <v>67.30698704729106</v>
+        <v>10.9373853951848</v>
       </c>
       <c r="E3" t="n">
-        <v>1.370167287237663</v>
+        <v>0.2226521841761206</v>
       </c>
       <c r="F3" t="n">
-        <v>1.498361431223657</v>
+        <v>0.2434837325738446</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
